--- a/frontend/test_data/header_detection/Wide_Valid_Messy_Metadata_Test.xlsx
+++ b/frontend/test_data/header_detection/Wide_Valid_Messy_Metadata_Test.xlsx
@@ -16509,7 +16509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:M200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16537,21 +16537,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -16587,15 +16584,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M2">
-        <v>46</v>
-      </c>
-      <c r="N2">
         <v>46</v>
       </c>
     </row>
@@ -16631,15 +16625,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M3">
-        <v>46</v>
-      </c>
-      <c r="N3">
         <v>46</v>
       </c>
     </row>
@@ -16675,15 +16666,12 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M4">
-        <v>46</v>
-      </c>
-      <c r="N4">
         <v>46</v>
       </c>
     </row>
@@ -16719,15 +16707,12 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M5">
-        <v>46</v>
-      </c>
-      <c r="N5">
         <v>46</v>
       </c>
     </row>
@@ -16763,15 +16748,12 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M6">
-        <v>103</v>
-      </c>
-      <c r="N6">
         <v>100</v>
       </c>
     </row>
@@ -16807,15 +16789,12 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M7">
-        <v>-57</v>
-      </c>
-      <c r="N7">
         <v>0</v>
       </c>
     </row>
@@ -16851,15 +16830,12 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M8">
-        <v>-57</v>
-      </c>
-      <c r="N8">
         <v>0</v>
       </c>
     </row>
@@ -16895,15 +16871,12 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M9">
-        <v>-57</v>
-      </c>
-      <c r="N9">
         <v>0</v>
       </c>
     </row>
@@ -16939,15 +16912,12 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M10">
-        <v>-57</v>
-      </c>
-      <c r="N10">
         <v>0</v>
       </c>
     </row>
@@ -16983,15 +16953,12 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M11">
-        <v>-57</v>
-      </c>
-      <c r="N11">
         <v>0</v>
       </c>
     </row>
@@ -17027,15 +16994,12 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L12">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M12">
-        <v>-57</v>
-      </c>
-      <c r="N12">
         <v>0</v>
       </c>
     </row>
@@ -17071,15 +17035,12 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L13">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M13">
-        <v>-57</v>
-      </c>
-      <c r="N13">
         <v>0</v>
       </c>
     </row>
@@ -17115,15 +17076,12 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L14">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M14">
-        <v>-57</v>
-      </c>
-      <c r="N14">
         <v>0</v>
       </c>
     </row>
@@ -17159,15 +17117,12 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L15">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M15">
-        <v>-57</v>
-      </c>
-      <c r="N15">
         <v>0</v>
       </c>
     </row>
@@ -17203,15 +17158,12 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L16">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M16">
-        <v>-57</v>
-      </c>
-      <c r="N16">
         <v>0</v>
       </c>
     </row>
@@ -17247,15 +17199,12 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L17">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M17">
-        <v>-57</v>
-      </c>
-      <c r="N17">
         <v>0</v>
       </c>
     </row>
@@ -17291,15 +17240,12 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L18">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M18">
-        <v>-57</v>
-      </c>
-      <c r="N18">
         <v>0</v>
       </c>
     </row>
@@ -17335,15 +17281,12 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L19">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M19">
-        <v>-57</v>
-      </c>
-      <c r="N19">
         <v>0</v>
       </c>
     </row>
@@ -17379,15 +17322,12 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L20">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M20">
-        <v>-57</v>
-      </c>
-      <c r="N20">
         <v>0</v>
       </c>
     </row>
@@ -17423,15 +17363,12 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L21">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M21">
-        <v>-57</v>
-      </c>
-      <c r="N21">
         <v>0</v>
       </c>
     </row>
@@ -17467,15 +17404,12 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L22">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M22">
-        <v>-57</v>
-      </c>
-      <c r="N22">
         <v>0</v>
       </c>
     </row>
@@ -17511,15 +17445,12 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L23">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M23">
-        <v>-57</v>
-      </c>
-      <c r="N23">
         <v>0</v>
       </c>
     </row>
@@ -17555,15 +17486,12 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L24">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M24">
-        <v>-57</v>
-      </c>
-      <c r="N24">
         <v>0</v>
       </c>
     </row>
@@ -17599,15 +17527,12 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L25">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M25">
-        <v>-57</v>
-      </c>
-      <c r="N25">
         <v>0</v>
       </c>
     </row>
@@ -17643,15 +17568,12 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L26">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M26">
-        <v>-57</v>
-      </c>
-      <c r="N26">
         <v>0</v>
       </c>
     </row>
@@ -17687,15 +17609,12 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L27">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M27">
-        <v>-57</v>
-      </c>
-      <c r="N27">
         <v>0</v>
       </c>
     </row>
@@ -17731,15 +17650,12 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L28">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M28">
-        <v>-57</v>
-      </c>
-      <c r="N28">
         <v>0</v>
       </c>
     </row>
@@ -17775,15 +17691,12 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L29">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M29">
-        <v>-57</v>
-      </c>
-      <c r="N29">
         <v>0</v>
       </c>
     </row>
@@ -17819,15 +17732,12 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L30">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M30">
-        <v>-57</v>
-      </c>
-      <c r="N30">
         <v>0</v>
       </c>
     </row>
@@ -17863,15 +17773,12 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L31">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M31">
-        <v>-57</v>
-      </c>
-      <c r="N31">
         <v>0</v>
       </c>
     </row>
@@ -17907,15 +17814,12 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L32">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M32">
-        <v>-57</v>
-      </c>
-      <c r="N32">
         <v>0</v>
       </c>
     </row>
@@ -17951,15 +17855,12 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L33">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M33">
-        <v>-57</v>
-      </c>
-      <c r="N33">
         <v>0</v>
       </c>
     </row>
@@ -17995,15 +17896,12 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L34">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M34">
-        <v>-57</v>
-      </c>
-      <c r="N34">
         <v>0</v>
       </c>
     </row>
@@ -18039,15 +17937,12 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L35">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M35">
-        <v>-57</v>
-      </c>
-      <c r="N35">
         <v>0</v>
       </c>
     </row>
@@ -18083,15 +17978,12 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L36">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M36">
-        <v>-57</v>
-      </c>
-      <c r="N36">
         <v>0</v>
       </c>
     </row>
@@ -18127,15 +18019,12 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L37">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M37">
-        <v>-57</v>
-      </c>
-      <c r="N37">
         <v>0</v>
       </c>
     </row>
@@ -18171,15 +18060,12 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M38">
-        <v>-57</v>
-      </c>
-      <c r="N38">
         <v>0</v>
       </c>
     </row>
@@ -18215,15 +18101,12 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L39">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M39">
-        <v>-57</v>
-      </c>
-      <c r="N39">
         <v>0</v>
       </c>
     </row>
@@ -18259,15 +18142,12 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L40">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M40">
-        <v>-57</v>
-      </c>
-      <c r="N40">
         <v>0</v>
       </c>
     </row>
@@ -18303,15 +18183,12 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L41">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M41">
-        <v>-57</v>
-      </c>
-      <c r="N41">
         <v>0</v>
       </c>
     </row>
@@ -18347,15 +18224,12 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L42">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M42">
-        <v>-57</v>
-      </c>
-      <c r="N42">
         <v>0</v>
       </c>
     </row>
@@ -18391,15 +18265,12 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L43">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M43">
-        <v>-57</v>
-      </c>
-      <c r="N43">
         <v>0</v>
       </c>
     </row>
@@ -18435,15 +18306,12 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L44">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M44">
-        <v>-57</v>
-      </c>
-      <c r="N44">
         <v>0</v>
       </c>
     </row>
@@ -18479,15 +18347,12 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L45">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M45">
-        <v>-57</v>
-      </c>
-      <c r="N45">
         <v>0</v>
       </c>
     </row>
@@ -18523,15 +18388,12 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L46">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M46">
-        <v>-57</v>
-      </c>
-      <c r="N46">
         <v>0</v>
       </c>
     </row>
@@ -18567,15 +18429,12 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L47">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M47">
-        <v>-57</v>
-      </c>
-      <c r="N47">
         <v>0</v>
       </c>
     </row>
@@ -18611,15 +18470,12 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L48">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M48">
-        <v>-57</v>
-      </c>
-      <c r="N48">
         <v>0</v>
       </c>
     </row>
@@ -18655,15 +18511,12 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L49">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M49">
-        <v>-57</v>
-      </c>
-      <c r="N49">
         <v>0</v>
       </c>
     </row>
@@ -18699,15 +18552,12 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L50">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M50">
-        <v>-57</v>
-      </c>
-      <c r="N50">
         <v>0</v>
       </c>
     </row>
@@ -18743,15 +18593,12 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L51">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M51">
-        <v>-57</v>
-      </c>
-      <c r="N51">
         <v>0</v>
       </c>
     </row>
@@ -18787,15 +18634,12 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L52">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M52">
-        <v>-57</v>
-      </c>
-      <c r="N52">
         <v>0</v>
       </c>
     </row>
@@ -18831,15 +18675,12 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L53">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M53">
-        <v>-57</v>
-      </c>
-      <c r="N53">
         <v>0</v>
       </c>
     </row>
@@ -18875,15 +18716,12 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L54">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M54">
-        <v>-57</v>
-      </c>
-      <c r="N54">
         <v>0</v>
       </c>
     </row>
@@ -18919,15 +18757,12 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L55">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M55">
-        <v>-57</v>
-      </c>
-      <c r="N55">
         <v>0</v>
       </c>
     </row>
@@ -18963,15 +18798,12 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L56">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M56">
-        <v>-57</v>
-      </c>
-      <c r="N56">
         <v>0</v>
       </c>
     </row>
@@ -19007,15 +18839,12 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L57">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M57">
-        <v>-57</v>
-      </c>
-      <c r="N57">
         <v>0</v>
       </c>
     </row>
@@ -19051,15 +18880,12 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L58">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M58">
-        <v>-57</v>
-      </c>
-      <c r="N58">
         <v>0</v>
       </c>
     </row>
@@ -19095,15 +18921,12 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L59">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M59">
-        <v>-57</v>
-      </c>
-      <c r="N59">
         <v>0</v>
       </c>
     </row>
@@ -19139,15 +18962,12 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L60">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M60">
-        <v>-57</v>
-      </c>
-      <c r="N60">
         <v>0</v>
       </c>
     </row>
@@ -19183,15 +19003,12 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L61">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M61">
-        <v>-57</v>
-      </c>
-      <c r="N61">
         <v>0</v>
       </c>
     </row>
@@ -19227,15 +19044,12 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L62">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M62">
-        <v>-57</v>
-      </c>
-      <c r="N62">
         <v>0</v>
       </c>
     </row>
@@ -19271,15 +19085,12 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L63">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M63">
-        <v>-57</v>
-      </c>
-      <c r="N63">
         <v>0</v>
       </c>
     </row>
@@ -19315,15 +19126,12 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L64">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M64">
-        <v>-57</v>
-      </c>
-      <c r="N64">
         <v>0</v>
       </c>
     </row>
@@ -19359,15 +19167,12 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L65">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M65">
-        <v>-57</v>
-      </c>
-      <c r="N65">
         <v>0</v>
       </c>
     </row>
@@ -19403,15 +19208,12 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L66">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M66">
-        <v>-57</v>
-      </c>
-      <c r="N66">
         <v>0</v>
       </c>
     </row>
@@ -19447,15 +19249,12 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L67">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M67">
-        <v>-57</v>
-      </c>
-      <c r="N67">
         <v>0</v>
       </c>
     </row>
@@ -19491,15 +19290,12 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L68">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M68">
-        <v>-57</v>
-      </c>
-      <c r="N68">
         <v>0</v>
       </c>
     </row>
@@ -19535,15 +19331,12 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M69">
-        <v>-57</v>
-      </c>
-      <c r="N69">
         <v>0</v>
       </c>
     </row>
@@ -19579,15 +19372,12 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L70">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M70">
-        <v>-57</v>
-      </c>
-      <c r="N70">
         <v>0</v>
       </c>
     </row>
@@ -19623,15 +19413,12 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M71">
-        <v>-57</v>
-      </c>
-      <c r="N71">
         <v>0</v>
       </c>
     </row>
@@ -19667,15 +19454,12 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L72">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M72">
-        <v>-57</v>
-      </c>
-      <c r="N72">
         <v>0</v>
       </c>
     </row>
@@ -19711,15 +19495,12 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L73">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M73">
-        <v>-57</v>
-      </c>
-      <c r="N73">
         <v>0</v>
       </c>
     </row>
@@ -19755,15 +19536,12 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L74">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M74">
-        <v>-57</v>
-      </c>
-      <c r="N74">
         <v>0</v>
       </c>
     </row>
@@ -19799,15 +19577,12 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L75">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M75">
-        <v>-57</v>
-      </c>
-      <c r="N75">
         <v>0</v>
       </c>
     </row>
@@ -19843,15 +19618,12 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L76">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M76">
-        <v>-57</v>
-      </c>
-      <c r="N76">
         <v>0</v>
       </c>
     </row>
@@ -19887,15 +19659,12 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L77">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M77">
-        <v>-57</v>
-      </c>
-      <c r="N77">
         <v>0</v>
       </c>
     </row>
@@ -19931,15 +19700,12 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L78">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M78">
-        <v>-57</v>
-      </c>
-      <c r="N78">
         <v>0</v>
       </c>
     </row>
@@ -19975,15 +19741,12 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L79">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M79">
-        <v>-57</v>
-      </c>
-      <c r="N79">
         <v>0</v>
       </c>
     </row>
@@ -20019,15 +19782,12 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L80">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M80">
-        <v>-57</v>
-      </c>
-      <c r="N80">
         <v>0</v>
       </c>
     </row>
@@ -20063,15 +19823,12 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L81">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M81">
-        <v>-57</v>
-      </c>
-      <c r="N81">
         <v>0</v>
       </c>
     </row>
@@ -20107,15 +19864,12 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L82">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M82">
-        <v>-57</v>
-      </c>
-      <c r="N82">
         <v>0</v>
       </c>
     </row>
@@ -20151,15 +19905,12 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L83">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M83">
-        <v>-57</v>
-      </c>
-      <c r="N83">
         <v>0</v>
       </c>
     </row>
@@ -20195,15 +19946,12 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L84">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M84">
-        <v>-57</v>
-      </c>
-      <c r="N84">
         <v>0</v>
       </c>
     </row>
@@ -20239,15 +19987,12 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L85">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M85">
-        <v>-57</v>
-      </c>
-      <c r="N85">
         <v>0</v>
       </c>
     </row>
@@ -20283,15 +20028,12 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L86">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M86">
-        <v>-57</v>
-      </c>
-      <c r="N86">
         <v>0</v>
       </c>
     </row>
@@ -20327,15 +20069,12 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L87">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M87">
-        <v>-57</v>
-      </c>
-      <c r="N87">
         <v>0</v>
       </c>
     </row>
@@ -20371,15 +20110,12 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L88">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M88">
-        <v>-57</v>
-      </c>
-      <c r="N88">
         <v>0</v>
       </c>
     </row>
@@ -20415,15 +20151,12 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L89">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M89">
-        <v>-57</v>
-      </c>
-      <c r="N89">
         <v>0</v>
       </c>
     </row>
@@ -20459,15 +20192,12 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L90">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M90">
-        <v>-57</v>
-      </c>
-      <c r="N90">
         <v>0</v>
       </c>
     </row>
@@ -20503,15 +20233,12 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L91">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M91">
-        <v>-57</v>
-      </c>
-      <c r="N91">
         <v>0</v>
       </c>
     </row>
@@ -20547,15 +20274,12 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L92">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M92">
-        <v>-57</v>
-      </c>
-      <c r="N92">
         <v>0</v>
       </c>
     </row>
@@ -20591,15 +20315,12 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L93">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M93">
-        <v>-57</v>
-      </c>
-      <c r="N93">
         <v>0</v>
       </c>
     </row>
@@ -20635,15 +20356,12 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L94">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M94">
-        <v>-57</v>
-      </c>
-      <c r="N94">
         <v>0</v>
       </c>
     </row>
@@ -20679,15 +20397,12 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L95">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M95">
-        <v>-57</v>
-      </c>
-      <c r="N95">
         <v>0</v>
       </c>
     </row>
@@ -20723,15 +20438,12 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L96">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M96">
-        <v>-57</v>
-      </c>
-      <c r="N96">
         <v>0</v>
       </c>
     </row>
@@ -20767,15 +20479,12 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L97">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M97">
-        <v>-57</v>
-      </c>
-      <c r="N97">
         <v>0</v>
       </c>
     </row>
@@ -20811,15 +20520,12 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L98">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M98">
-        <v>-57</v>
-      </c>
-      <c r="N98">
         <v>0</v>
       </c>
     </row>
@@ -20855,15 +20561,12 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L99">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M99">
-        <v>-57</v>
-      </c>
-      <c r="N99">
         <v>0</v>
       </c>
     </row>
@@ -20899,15 +20602,12 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L100">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M100">
-        <v>-57</v>
-      </c>
-      <c r="N100">
         <v>0</v>
       </c>
     </row>
@@ -20943,15 +20643,12 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L101">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M101">
-        <v>-57</v>
-      </c>
-      <c r="N101">
         <v>0</v>
       </c>
     </row>
@@ -20987,15 +20684,12 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L102">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M102">
-        <v>-57</v>
-      </c>
-      <c r="N102">
         <v>0</v>
       </c>
     </row>
@@ -21031,15 +20725,12 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L103">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M103">
-        <v>-57</v>
-      </c>
-      <c r="N103">
         <v>0</v>
       </c>
     </row>
@@ -21075,15 +20766,12 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L104">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M104">
-        <v>-57</v>
-      </c>
-      <c r="N104">
         <v>0</v>
       </c>
     </row>
@@ -21119,15 +20807,12 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L105">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M105">
-        <v>-57</v>
-      </c>
-      <c r="N105">
         <v>0</v>
       </c>
     </row>
@@ -21163,15 +20848,12 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L106">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M106">
-        <v>-57</v>
-      </c>
-      <c r="N106">
         <v>0</v>
       </c>
     </row>
@@ -21207,15 +20889,12 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L107">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M107">
-        <v>-57</v>
-      </c>
-      <c r="N107">
         <v>0</v>
       </c>
     </row>
@@ -21251,15 +20930,12 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L108">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M108">
-        <v>-57</v>
-      </c>
-      <c r="N108">
         <v>0</v>
       </c>
     </row>
@@ -21295,15 +20971,12 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L109">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M109">
-        <v>-57</v>
-      </c>
-      <c r="N109">
         <v>0</v>
       </c>
     </row>
@@ -21339,15 +21012,12 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L110">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M110">
-        <v>-57</v>
-      </c>
-      <c r="N110">
         <v>0</v>
       </c>
     </row>
@@ -21383,15 +21053,12 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L111">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M111">
-        <v>-57</v>
-      </c>
-      <c r="N111">
         <v>0</v>
       </c>
     </row>
@@ -21427,15 +21094,12 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L112">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M112">
-        <v>-57</v>
-      </c>
-      <c r="N112">
         <v>0</v>
       </c>
     </row>
@@ -21471,15 +21135,12 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L113">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M113">
-        <v>-57</v>
-      </c>
-      <c r="N113">
         <v>0</v>
       </c>
     </row>
@@ -21515,15 +21176,12 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L114">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M114">
-        <v>-57</v>
-      </c>
-      <c r="N114">
         <v>0</v>
       </c>
     </row>
@@ -21559,15 +21217,12 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L115">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M115">
-        <v>-57</v>
-      </c>
-      <c r="N115">
         <v>0</v>
       </c>
     </row>
@@ -21603,15 +21258,12 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L116">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M116">
-        <v>-57</v>
-      </c>
-      <c r="N116">
         <v>0</v>
       </c>
     </row>
@@ -21647,15 +21299,12 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L117">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M117">
-        <v>-57</v>
-      </c>
-      <c r="N117">
         <v>0</v>
       </c>
     </row>
@@ -21691,15 +21340,12 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L118">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M118">
-        <v>-57</v>
-      </c>
-      <c r="N118">
         <v>0</v>
       </c>
     </row>
@@ -21735,15 +21381,12 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L119">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M119">
-        <v>-57</v>
-      </c>
-      <c r="N119">
         <v>0</v>
       </c>
     </row>
@@ -21779,15 +21422,12 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L120">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M120">
-        <v>-57</v>
-      </c>
-      <c r="N120">
         <v>0</v>
       </c>
     </row>
@@ -21823,15 +21463,12 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L121">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M121">
-        <v>-57</v>
-      </c>
-      <c r="N121">
         <v>0</v>
       </c>
     </row>
@@ -21867,15 +21504,12 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L122">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M122">
-        <v>-57</v>
-      </c>
-      <c r="N122">
         <v>0</v>
       </c>
     </row>
@@ -21911,15 +21545,12 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L123">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M123">
-        <v>-57</v>
-      </c>
-      <c r="N123">
         <v>0</v>
       </c>
     </row>
@@ -21955,15 +21586,12 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L124">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M124">
-        <v>-57</v>
-      </c>
-      <c r="N124">
         <v>0</v>
       </c>
     </row>
@@ -21999,15 +21627,12 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L125">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M125">
-        <v>-57</v>
-      </c>
-      <c r="N125">
         <v>0</v>
       </c>
     </row>
@@ -22043,15 +21668,12 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L126">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M126">
-        <v>-57</v>
-      </c>
-      <c r="N126">
         <v>0</v>
       </c>
     </row>
@@ -22087,15 +21709,12 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L127">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M127">
-        <v>-57</v>
-      </c>
-      <c r="N127">
         <v>0</v>
       </c>
     </row>
@@ -22131,15 +21750,12 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L128">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M128">
-        <v>-57</v>
-      </c>
-      <c r="N128">
         <v>0</v>
       </c>
     </row>
@@ -22175,15 +21791,12 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L129">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M129">
-        <v>-57</v>
-      </c>
-      <c r="N129">
         <v>0</v>
       </c>
     </row>
@@ -22219,15 +21832,12 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L130">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M130">
-        <v>-57</v>
-      </c>
-      <c r="N130">
         <v>0</v>
       </c>
     </row>
@@ -22263,15 +21873,12 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L131">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M131">
-        <v>-57</v>
-      </c>
-      <c r="N131">
         <v>0</v>
       </c>
     </row>
@@ -22307,15 +21914,12 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L132">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M132">
-        <v>-57</v>
-      </c>
-      <c r="N132">
         <v>0</v>
       </c>
     </row>
@@ -22351,15 +21955,12 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L133">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M133">
-        <v>-57</v>
-      </c>
-      <c r="N133">
         <v>0</v>
       </c>
     </row>
@@ -22395,15 +21996,12 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L134">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M134">
-        <v>-57</v>
-      </c>
-      <c r="N134">
         <v>0</v>
       </c>
     </row>
@@ -22439,15 +22037,12 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L135">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M135">
-        <v>-57</v>
-      </c>
-      <c r="N135">
         <v>0</v>
       </c>
     </row>
@@ -22483,15 +22078,12 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L136">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M136">
-        <v>-57</v>
-      </c>
-      <c r="N136">
         <v>0</v>
       </c>
     </row>
@@ -22527,15 +22119,12 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L137">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M137">
-        <v>-57</v>
-      </c>
-      <c r="N137">
         <v>0</v>
       </c>
     </row>
@@ -22571,15 +22160,12 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L138">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M138">
-        <v>-57</v>
-      </c>
-      <c r="N138">
         <v>0</v>
       </c>
     </row>
@@ -22615,15 +22201,12 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L139">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M139">
-        <v>-57</v>
-      </c>
-      <c r="N139">
         <v>0</v>
       </c>
     </row>
@@ -22659,15 +22242,12 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L140">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M140">
-        <v>-57</v>
-      </c>
-      <c r="N140">
         <v>0</v>
       </c>
     </row>
@@ -22703,15 +22283,12 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L141">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M141">
-        <v>-57</v>
-      </c>
-      <c r="N141">
         <v>0</v>
       </c>
     </row>
@@ -22747,15 +22324,12 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L142">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M142">
-        <v>-57</v>
-      </c>
-      <c r="N142">
         <v>0</v>
       </c>
     </row>
@@ -22791,15 +22365,12 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L143">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M143">
-        <v>-57</v>
-      </c>
-      <c r="N143">
         <v>0</v>
       </c>
     </row>
@@ -22835,15 +22406,12 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L144">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M144">
-        <v>-57</v>
-      </c>
-      <c r="N144">
         <v>0</v>
       </c>
     </row>
@@ -22879,15 +22447,12 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L145">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M145">
-        <v>-57</v>
-      </c>
-      <c r="N145">
         <v>0</v>
       </c>
     </row>
@@ -22923,15 +22488,12 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L146">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M146">
-        <v>-57</v>
-      </c>
-      <c r="N146">
         <v>0</v>
       </c>
     </row>
@@ -22967,15 +22529,12 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L147">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M147">
-        <v>-57</v>
-      </c>
-      <c r="N147">
         <v>0</v>
       </c>
     </row>
@@ -23011,15 +22570,12 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L148">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M148">
-        <v>-57</v>
-      </c>
-      <c r="N148">
         <v>0</v>
       </c>
     </row>
@@ -23055,15 +22611,12 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L149">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M149">
-        <v>-57</v>
-      </c>
-      <c r="N149">
         <v>0</v>
       </c>
     </row>
@@ -23099,15 +22652,12 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L150">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M150">
-        <v>-57</v>
-      </c>
-      <c r="N150">
         <v>0</v>
       </c>
     </row>
@@ -23143,15 +22693,12 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L151">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M151">
-        <v>-57</v>
-      </c>
-      <c r="N151">
         <v>0</v>
       </c>
     </row>
@@ -23187,15 +22734,12 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L152">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M152">
-        <v>-57</v>
-      </c>
-      <c r="N152">
         <v>0</v>
       </c>
     </row>
@@ -23231,15 +22775,12 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L153">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M153">
-        <v>-57</v>
-      </c>
-      <c r="N153">
         <v>0</v>
       </c>
     </row>
@@ -23275,15 +22816,12 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L154">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M154">
-        <v>-57</v>
-      </c>
-      <c r="N154">
         <v>0</v>
       </c>
     </row>
@@ -23319,15 +22857,12 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L155">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M155">
-        <v>-57</v>
-      </c>
-      <c r="N155">
         <v>0</v>
       </c>
     </row>
@@ -23363,15 +22898,12 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L156">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M156">
-        <v>-57</v>
-      </c>
-      <c r="N156">
         <v>0</v>
       </c>
     </row>
@@ -23407,15 +22939,12 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L157">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M157">
-        <v>-57</v>
-      </c>
-      <c r="N157">
         <v>0</v>
       </c>
     </row>
@@ -23451,15 +22980,12 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L158">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M158">
-        <v>-57</v>
-      </c>
-      <c r="N158">
         <v>0</v>
       </c>
     </row>
@@ -23495,15 +23021,12 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L159">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M159">
-        <v>-57</v>
-      </c>
-      <c r="N159">
         <v>0</v>
       </c>
     </row>
@@ -23539,15 +23062,12 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L160">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M160">
-        <v>-57</v>
-      </c>
-      <c r="N160">
         <v>0</v>
       </c>
     </row>
@@ -23583,15 +23103,12 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L161">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M161">
-        <v>-57</v>
-      </c>
-      <c r="N161">
         <v>0</v>
       </c>
     </row>
@@ -23627,15 +23144,12 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L162">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M162">
-        <v>-57</v>
-      </c>
-      <c r="N162">
         <v>0</v>
       </c>
     </row>
@@ -23671,15 +23185,12 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L163">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M163">
-        <v>-57</v>
-      </c>
-      <c r="N163">
         <v>0</v>
       </c>
     </row>
@@ -23715,15 +23226,12 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L164">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M164">
-        <v>-57</v>
-      </c>
-      <c r="N164">
         <v>0</v>
       </c>
     </row>
@@ -23759,15 +23267,12 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L165">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M165">
-        <v>-57</v>
-      </c>
-      <c r="N165">
         <v>0</v>
       </c>
     </row>
@@ -23803,15 +23308,12 @@
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L166">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M166">
-        <v>-57</v>
-      </c>
-      <c r="N166">
         <v>0</v>
       </c>
     </row>
@@ -23844,18 +23346,15 @@
         <v>0</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K167">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L167">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M167">
-        <v>-67</v>
-      </c>
-      <c r="N167">
         <v>0</v>
       </c>
     </row>
@@ -23888,18 +23387,15 @@
         <v>0</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K168">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L168">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M168">
-        <v>-67</v>
-      </c>
-      <c r="N168">
         <v>0</v>
       </c>
     </row>
@@ -23932,18 +23428,15 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K169">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L169">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M169">
-        <v>-67</v>
-      </c>
-      <c r="N169">
         <v>0</v>
       </c>
     </row>
@@ -23976,18 +23469,15 @@
         <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K170">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L170">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M170">
-        <v>-67</v>
-      </c>
-      <c r="N170">
         <v>0</v>
       </c>
     </row>
@@ -24020,18 +23510,15 @@
         <v>0</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K171">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L171">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M171">
-        <v>-67</v>
-      </c>
-      <c r="N171">
         <v>0</v>
       </c>
     </row>
@@ -24064,18 +23551,15 @@
         <v>0</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K172">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L172">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M172">
-        <v>-67</v>
-      </c>
-      <c r="N172">
         <v>0</v>
       </c>
     </row>
@@ -24108,18 +23592,15 @@
         <v>0</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K173">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L173">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M173">
-        <v>-67</v>
-      </c>
-      <c r="N173">
         <v>0</v>
       </c>
     </row>
@@ -24152,18 +23633,15 @@
         <v>0</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K174">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L174">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M174">
-        <v>-67</v>
-      </c>
-      <c r="N174">
         <v>0</v>
       </c>
     </row>
@@ -24196,18 +23674,15 @@
         <v>0</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K175">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L175">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M175">
-        <v>-67</v>
-      </c>
-      <c r="N175">
         <v>0</v>
       </c>
     </row>
@@ -24240,18 +23715,15 @@
         <v>0</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K176">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L176">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M176">
-        <v>-67</v>
-      </c>
-      <c r="N176">
         <v>0</v>
       </c>
     </row>
@@ -24284,18 +23756,15 @@
         <v>0</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K177">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L177">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M177">
-        <v>-67</v>
-      </c>
-      <c r="N177">
         <v>0</v>
       </c>
     </row>
@@ -24328,18 +23797,15 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K178">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L178">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M178">
-        <v>-67</v>
-      </c>
-      <c r="N178">
         <v>0</v>
       </c>
     </row>
@@ -24372,18 +23838,15 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K179">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L179">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M179">
-        <v>-67</v>
-      </c>
-      <c r="N179">
         <v>0</v>
       </c>
     </row>
@@ -24416,18 +23879,15 @@
         <v>0</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K180">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L180">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M180">
-        <v>-67</v>
-      </c>
-      <c r="N180">
         <v>0</v>
       </c>
     </row>
@@ -24460,18 +23920,15 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K181">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L181">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M181">
-        <v>-67</v>
-      </c>
-      <c r="N181">
         <v>0</v>
       </c>
     </row>
@@ -24504,18 +23961,15 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K182">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L182">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M182">
-        <v>-67</v>
-      </c>
-      <c r="N182">
         <v>0</v>
       </c>
     </row>
@@ -24548,18 +24002,15 @@
         <v>0</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K183">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L183">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M183">
-        <v>-67</v>
-      </c>
-      <c r="N183">
         <v>0</v>
       </c>
     </row>
@@ -24592,18 +24043,15 @@
         <v>0</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K184">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L184">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M184">
-        <v>-67</v>
-      </c>
-      <c r="N184">
         <v>0</v>
       </c>
     </row>
@@ -24636,18 +24084,15 @@
         <v>0</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K185">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L185">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M185">
-        <v>-67</v>
-      </c>
-      <c r="N185">
         <v>0</v>
       </c>
     </row>
@@ -24680,18 +24125,15 @@
         <v>0</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K186">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L186">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M186">
-        <v>-67</v>
-      </c>
-      <c r="N186">
         <v>0</v>
       </c>
     </row>
@@ -24724,18 +24166,15 @@
         <v>0</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K187">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L187">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M187">
-        <v>-67</v>
-      </c>
-      <c r="N187">
         <v>0</v>
       </c>
     </row>
@@ -24768,18 +24207,15 @@
         <v>0</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K188">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L188">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M188">
-        <v>-67</v>
-      </c>
-      <c r="N188">
         <v>0</v>
       </c>
     </row>
@@ -24812,18 +24248,15 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K189">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L189">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M189">
-        <v>-67</v>
-      </c>
-      <c r="N189">
         <v>0</v>
       </c>
     </row>
@@ -24856,18 +24289,15 @@
         <v>0</v>
       </c>
       <c r="J190">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K190">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L190">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M190">
-        <v>-67</v>
-      </c>
-      <c r="N190">
         <v>0</v>
       </c>
     </row>
@@ -24900,18 +24330,15 @@
         <v>0</v>
       </c>
       <c r="J191">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K191">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L191">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M191">
-        <v>-67</v>
-      </c>
-      <c r="N191">
         <v>0</v>
       </c>
     </row>
@@ -24944,18 +24371,15 @@
         <v>0</v>
       </c>
       <c r="J192">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K192">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L192">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M192">
-        <v>-67</v>
-      </c>
-      <c r="N192">
         <v>0</v>
       </c>
     </row>
@@ -24988,18 +24412,15 @@
         <v>0</v>
       </c>
       <c r="J193">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K193">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L193">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M193">
-        <v>-67</v>
-      </c>
-      <c r="N193">
         <v>0</v>
       </c>
     </row>
@@ -25032,18 +24453,15 @@
         <v>0</v>
       </c>
       <c r="J194">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K194">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L194">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M194">
-        <v>-67</v>
-      </c>
-      <c r="N194">
         <v>0</v>
       </c>
     </row>
@@ -25076,18 +24494,15 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K195">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L195">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M195">
-        <v>-67</v>
-      </c>
-      <c r="N195">
         <v>0</v>
       </c>
     </row>
@@ -25120,18 +24535,15 @@
         <v>0</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K196">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L196">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M196">
-        <v>-67</v>
-      </c>
-      <c r="N196">
         <v>0</v>
       </c>
     </row>
@@ -25164,18 +24576,15 @@
         <v>0</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K197">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L197">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M197">
-        <v>-67</v>
-      </c>
-      <c r="N197">
         <v>0</v>
       </c>
     </row>
@@ -25208,18 +24617,15 @@
         <v>0</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K198">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L198">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M198">
-        <v>-67</v>
-      </c>
-      <c r="N198">
         <v>0</v>
       </c>
     </row>
@@ -25252,18 +24658,15 @@
         <v>0</v>
       </c>
       <c r="J199">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K199">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L199">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M199">
-        <v>-67</v>
-      </c>
-      <c r="N199">
         <v>0</v>
       </c>
     </row>
@@ -25296,24 +24699,21 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K200">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L200">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M200">
-        <v>-67</v>
-      </c>
-      <c r="N200">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M200"/>
   </ignoredErrors>
 </worksheet>
 </file>